--- a/www/download/IND.gdp.s.us.EXI382.xlsx
+++ b/www/download/IND.gdp.s.us.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>189175.257540555</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>229068.41598323</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>263100.724337554</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>227966.974078219</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>272707.534523982</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>294860.199458775</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>296521.503764644</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>302169.362993172</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>319963.637909036</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>347917.147415736</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>389943.603188172</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>417901.327888781</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>448597.586269142</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>447017.556869721</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>455911.404798483</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>596922.955377341</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>677672.10896567</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>739229.98518753</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>702722.087418966</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>681784.693964548</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>693992.913896224</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>721901.895549783</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>761915.825739058</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>744663.657377709</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>741471.400513113</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>761412.861194616</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>775474.127776046</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>137776.102702318</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>138675.65576445</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>149405.448353334</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>154829.386734769</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>163443.997005056</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>159989.859012893</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>169392.18197627</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>176623.950797295</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>178159.705298358</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>182675.26448117</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>196836.502666927</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>206567.522234995</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>208564.263984617</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>212888.113132108</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>226457.791721526</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>232813.831267302</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>242565.766204408</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>236566.826142086</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>246091.867444322</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>250811.873116411</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>257859.396399497</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>280593.997932669</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>289743.29863971</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>318524.912685814</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>316793.732902749</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>320332.319547597</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>318047.186050308</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>172806.269142529</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>171610.681531188</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>177814.747913651</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>178729.614164472</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>194092.042918714</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>191364.135608403</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>206175.841604781</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>218393.089654858</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>223416.790602962</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>231207.957562803</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>255490.295363794</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>255247.215088924</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>271420.186247473</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>265932.769357667</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>292420.11075556</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>283766.461550859</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>288284.191040991</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>296215.577721739</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>300898.938191442</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>302816.394501296</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>314015.141556687</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>325194.797857661</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>337803.074531051</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>349246.902140598</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>356728.274200096</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>361787.166312345</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>367667.745740041</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7412.59685507332</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4275.84851873013</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5395.39324198548</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7600.9187182648</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7263.81201336957</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8278.65784178765</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8944.30587964316</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>9116.92651824268</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>10583.8256687442</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11695.9482368203</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13795.6419466615</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>16855.8023622092</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>19359.9562950984</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>23140.4394916659</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>22787.1266028911</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>23575.4974033476</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>25979.9344588617</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>26574.6366105645</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>26270.1146722125</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>27749.7023691494</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>29548.4807157118</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>31972.8656272604</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>31787.3777960546</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>37610.160654865</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>40491.6783114033</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>43160.6282093114</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>43027.5932335813</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>421565.422642747</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>483324.293932423</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>535967.730572956</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>536826.710079462</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>396676.192655714</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>486956.597160369</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>439450.187460806</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>375434.966158984</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>337046.540318879</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>364706.746068484</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>484775.129798719</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>598661.385049562</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>711401.386589173</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>818885.867410992</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>871371.317694379</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>1217981.59964033</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>1376884.77468782</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>1404327.38368828</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>1362051.56420674</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>1353028.92271325</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>1199703.39782009</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1204219.23288698</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>1346252.38105513</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>1194626.44085582</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>1214636.15785366</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1235134.042775</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>1289076.68445808</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>371768.709658813</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>384223.199151082</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>446183.775044952</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>442820.354917973</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>534448.206600535</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>662928.418342188</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>688645.159251259</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>670434.481200263</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>656244.315456864</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>638925.802771378</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>699704.548443422</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>785496.672151324</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>813187.112296147</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>784286.139216793</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>758068.534774726</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>932395.975602146</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>1040143.58283661</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>1085521.57984688</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>1106048.06881074</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>1028895.54282362</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>1133727.55949607</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>1072605.24958314</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>1177909.06645054</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1178289.97346366</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1342114.23532408</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>1302273.64695299</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>1192394.70114042</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>400329.470850965</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>476778.751787288</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>663920.598646427</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>695282.449997384</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>768035.754687623</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>1077282.99802718</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>1232996.2925737</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>1245214.72167468</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>1172913.29077283</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>1203124.77921863</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>1453551.37880142</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>1707303.85105494</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.118</t>
+          <t>1964338.87076501</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.335</t>
+          <t>2422618.80054288</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.722</t>
+          <t>3005304.78928922</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>3920481.98279141</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2.748</t>
+          <t>4743891.51111273</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3.175</t>
+          <t>5723822.74001907</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3.678</t>
+          <t>6469329.28826708</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3.876</t>
+          <t>6866163.33823258</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>4.874</t>
+          <t>8681895.99737783</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4.916</t>
+          <t>8781656.92961192</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>5.377</t>
+          <t>9645527.18650645</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.645</t>
+          <t>10088155.3306304</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>10907656.2223546</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>6.503</t>
+          <t>11569627.1546086</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>12234705.201168</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4371.57306371842</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4877.86784214894</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5008.72235657054</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6195.92016023624</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6275.90556441137</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7419.85046600106</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7040.88059388494</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7393.48427464548</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8845.065016218</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8635.13236929557</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9719.05576583727</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10835.6258268921</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11528.210915773</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11419.375598685</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11696.1831953596</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11408.8484840956</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11292.7231458168</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11086.3383922183</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11317.5648239052</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9507.56698760539</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10256.0137159192</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11566.7853112412</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10652.6654111459</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12048.3429253252</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12959.6974173001</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12288.1503574079</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>14284.43341825</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>26082.9540793907</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>29230.8171605553</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>32948.3902244163</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>33445.008255105</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>33312.2803937688</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>35341.6007526238</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>41557.4000873706</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>48008.5891682908</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>49104.2546616194</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>53985.1802059316</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>63579.7749834471</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>71897.2911964587</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>80355.9463756802</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>93974.7898271657</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>84375.895073168</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>90403.359691912</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>91187.0546874407</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>93402.7279033571</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>91963.9268428209</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>89371.0557697606</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>96966.3176092888</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>101779.436427111</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>109770.608685164</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>122545.94550835</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>130951.552256181</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>131426.589869032</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>138316.937589771</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1368157.60468325</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.123</t>
+          <t>1354652.74774401</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1352565.39536997</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>1375223.85786684</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>1427225.26942683</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>1475951.62023184</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.185</t>
+          <t>1447296.04478334</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.229</t>
+          <t>1488344.06795803</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>1673842.43500128</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1534048.43455075</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1520826.82026448</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>1571812.49410633</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1631639.32634152</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1649846.67240815</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1640759.92983195</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1691519.13776875</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1759292.34428977</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1790405.09129841</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.528</t>
+          <t>1846103.62629726</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1922500.10321682</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1945559.91267858</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2001244.8288935</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2119987.9723268</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.832</t>
+          <t>2224220.08619445</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2224404.38257006</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>2279053.23714022</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>2283598.01827504</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>96060.4446752403</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>99925.4032742949</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>103091.209702738</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>105339.299944049</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>118193.632245162</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>126615.405654907</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>131368.701216377</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>137998.617763696</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>141198.007553517</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>145317.257887552</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>151328.163021267</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>163244.369496257</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>173730.973966957</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>177938.161147552</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>173850.883858995</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>178800.320239999</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>181704.405426361</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>187087.87920909</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>200210.004509508</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>207926.424878804</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>215525.038888096</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>224905.123828361</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>234193.461282825</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>220829.085465618</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>217590.100410967</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>242668.464354967</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>254643.4334717</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>260509.777612203</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>284179.985901746</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>290278.957029927</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>321075.104292366</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>348012.140021471</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>383785.679510459</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>417507.472885858</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>445928.079913591</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>466802.96455133</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>497597.667025685</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>540731.334506873</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>580854.811044142</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>607610.867270418</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>663469.240934069</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>613234.278291308</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>618140.623543395</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>611392.85004188</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>594007.483071682</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>588619.148847485</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>593240.594263298</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>627363.176581258</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>647099.634472076</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>688456.241731773</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>717107.838366861</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>718831.200932094</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>735390.932981204</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>837472.893485185</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2493.96320206664</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2698.17050070333</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3394.70406861015</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3435.49941169986</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3410.75815817332</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4094.00704317307</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4181.30291714862</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4963.47067623324</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5536.00005679018</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5492.49704696846</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6885.48786610167</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8383.17522350598</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10269.1501111067</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10767.2688974591</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10070.1710040397</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9448.67981628369</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11362.8167380888</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11710.3057004458</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12420.1502917095</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>12707.9667398408</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13237.5595519225</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14737.8662324974</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>14971.6543872427</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>16876.8554311544</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>17987.0377854774</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>18388.4266766552</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>18927.2228107651</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>52650.917434092</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56539.2377763761</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>60326.5586879035</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>63465.3464183315</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>65673.9425376231</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>71054.7300975611</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76239.6198597981</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78462.0598962817</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81553.4331246336</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83439.3579139732</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>88203.3762400658</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90852.3159429836</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96660.5038075269</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>105710.812287551</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103164.853091084</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103647.86548049</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109336.660534451</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>112021.698725256</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113679.814729037</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116600.870908694</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119516.341432885</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>122672.23093261</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129586.837309993</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>150537.526651832</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>135596.050961941</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>145492.146234474</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>159551.790372201</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>732428.932133043</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>740962.727009892</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>752171.083712088</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>728825.551824792</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>859391.968858819</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>852925.76050881</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>888162.676510331</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>921766.387280169</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>954686.886287677</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>994971.641724049</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>1031448.9238495</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>1050719.08305417</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1148139.58009825</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1159077.07870834</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1132599.91792235</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>1181279.97621561</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1212979.22090558</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1253597.4742938</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1264928.63713457</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1292264.30575139</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.271</t>
+          <t>1323985.6109435</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1.351</t>
+          <t>1417836.66103998</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>1.309</t>
+          <t>1367241.24470062</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.369</t>
+          <t>1422330.43152057</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1461576.17939829</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1560883.44551979</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1.508</t>
+          <t>1575349.92803172</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>854976.28285482</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>921792.484952967</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>1134973.78659673</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>1235026.27145142</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>1349245.93179492</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>1556478.96924398</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1584937.24995105</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1631787.51002303</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1566811.6349297</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.147</t>
+          <t>1667883.60475486</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1744795.63185621</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1833188.23980859</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1914900.24168434</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1681836.83574906</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.052</t>
+          <t>1516898.94643804</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>1638995.29677145</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1662286.85746881</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1812298.70286409</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1808827.6413501</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1995992.58596611</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.586</t>
+          <t>2310675.40907422</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>2083356.15020749</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>2045466.9596099</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>2118468.01160666</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.521</t>
+          <t>2213342.20548565</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>2247451.69981159</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>2279101.58595894</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>38327.0621713343</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>45624.2460690881</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48349.7806323788</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48915.438556528</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50955.377307199</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56509.045434385</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>57676.2759734772</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>65809.1279687802</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69184.1825538888</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75125.1476527608</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>76757.3285795363</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84938.8481195993</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92205.3843781715</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96029.0785367632</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>94384.0233582427</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>91928.3654514744</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>80013.7874332555</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74130.5597386659</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>73305.323922189</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>71144.1698642243</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>68976.1152932261</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>66816.8801942598</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>70655.9571287731</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70166.9871922584</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71422.4788395626</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65211.7771268116</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74275.9031271737</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17470.5581967425</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18893.1863402378</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20541.4990627006</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21640.503267145</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>22413.7388294894</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>25213.7531879348</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>31149.0714279044</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>33949.1950648368</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>39169.8153917607</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>43908.0633268092</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>46941.7676761457</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>48393.17484152</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>54198.3641729286</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>57934.096081321</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>51422.5548888028</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>53613.3688948527</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>55399.5064420902</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>53941.0255082769</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>55402.8298076972</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>57553.7574018931</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>61719.5607284224</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>63040.5215704731</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>69627.064626734</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>78312.9246891692</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>81061.1405702904</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>86411.4829497408</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>89315.7414914946</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>210712.333724318</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>227837.51441964</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>269668.913841382</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>283068.627648492</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>325703.731342495</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>393335.65828407</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>421028.58395745</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>418225.354950057</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>411619.747339733</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>444842.132317808</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>521736.900990508</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>597273.20251814</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>689298.106816933</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>686813.969257674</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>741678.602342143</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>996938.026146487</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>1075277.24227945</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1155387.21476827</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>1149089.07974069</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>1219601.24039577</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>1533038.71617379</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>1652901.13823071</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1.094</t>
+          <t>1856953.79154826</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>1839348.06357765</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>2002194.06175588</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>2173609.80899672</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2377787.86076033</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>95934.0670913138</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>108567.009510986</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>118558.577909264</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>50591.2868739386</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>76728.1000630814</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>91906.7797516557</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>92249.1684480023</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>104636.016967952</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>112851.921509286</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>105402.832955366</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>113146.980905888</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>135587.204229629</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>149800.091128433</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>167006.452380209</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>198855.189593922</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>274261.958858071</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>286747.178976284</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>336727.209283955</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>294493.848730857</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>291742.745753372</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>341086.197406537</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>371540.361266656</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>385283.339111425</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>377410.407806283</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>438692.241271152</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>466718.519378898</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>490223.018781063</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32302.7984823735</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>36093.4360236444</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>44066.9872558084</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>48680.067156549</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>53933.4730465876</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>63082.0730331958</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>70444.5401210462</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>73023.8720282549</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>86318.7917360232</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>89257.6176575723</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>97214.3587173002</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>107522.502879033</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>114716.473360745</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>114014.868434016</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>118175.562837178</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>98850.8091078869</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>103757.493106292</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>100582.346682841</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>104671.793776018</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>111413.729096065</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>144224.986032919</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>149941.781566274</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>172755.730351576</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>182402.52999974</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>214625.685206984</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>224410.128928064</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>218437.51193459</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>651649.271034766</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>750894.237085948</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>798278.36081248</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.564</t>
+          <t>792616.998208279</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>850609.504966515</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>898575.576185548</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>933860.986858833</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>966625.928730204</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1007245.65502225</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>1038644.5210592</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>1067708.7566784</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>1111386.69629005</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>1152764.98763127</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>1155923.32439856</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>1120451.33817705</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1161386.29988015</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1173696.47649374</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>1155895.67317211</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1144302.1948695</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>1186401.71342753</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>1209303.34228121</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>1206164.8051348</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>1275242.45411382</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1276087.6049788</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1317280.75836659</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>1296845.23871968</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>0.978</t>
+          <t>1331090.6893819</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2.532</t>
+          <t>4119198.25299078</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>3605575.88811016</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>3691101.4897913</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>3446671.1141339</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.516</t>
+          <t>4080355.08878247</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>5363573.23332861</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.938</t>
+          <t>4787414.66891026</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>4078096.72886439</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.232</t>
+          <t>3612270.66925794</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.159</t>
+          <t>3511159.7056319</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3699584.39059906</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>3509702.3324658</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.798</t>
+          <t>2933991.76945508</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.971</t>
+          <t>3335816.45500757</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.206</t>
+          <t>3585503.73410666</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.462</t>
+          <t>4041960.75627114</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2.566</t>
+          <t>4187075.69679185</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>4459812.67479589</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>3414459.58798674</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>3406577.72777483</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>3703096.36332747</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2.343</t>
+          <t>3859069.49923248</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2.188</t>
+          <t>3669015.05812505</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>2.215</t>
+          <t>3647585.51270002</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2.397</t>
+          <t>3946970.15320514</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2.409</t>
+          <t>3965892.08112325</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2.559</t>
+          <t>4217417.17808272</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>316275.560538257</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>341426.001832835</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>349598.499617468</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>233316.21150129</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>317624.859034787</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>431535.20800052</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>418858.755094578</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>451278.21564484</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>447195.247601573</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>452048.178070333</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>534680.402334596</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>617255.402744607</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>612579.348697739</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>511527.183093146</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>488020.121485369</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>608399.331502583</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>623151.235772081</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>702299.028305716</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>747398.20656357</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>745547.378146038</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>934680.524813499</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>0.629</t>
+          <t>959464.59311781</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>1098009.58184404</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>984578.054481153</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1038624.25527945</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>1062560.5206201</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>1102227.30018749</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3185.62803299093</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3890.01479010425</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5253.84379162834</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5962.82075160565</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6528.29988547634</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7296.50197862394</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7462.52858531726</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9170.65672044465</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9788.58966478783</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10805.0549013059</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12816.7280499287</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>15174.316622427</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>18398.7953417805</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>20078.8197636842</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>16891.3603161131</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>15648.073316843</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>17798.8216947941</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>19013.4680443279</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>19188.144709095</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>20316.591672051</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>21885.5066591948</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>22739.0317043408</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>25063.6901840341</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>27737.2539987008</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>28523.9062123854</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>28726.6458203556</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>30466.6995932318</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11376.9877159211</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11459.5728223519</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12232.9386404125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12124.0824405057</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>14021.9025397447</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>15103.2445010557</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>16309.3021318069</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>15894.7805435406</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>17146.4912025201</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>17116.6484510259</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>19994.5708848269</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>20141.8570878332</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>21901.04945079</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>24963.5052401376</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>24733.8933727091</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>26191.3190380865</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>25446.2209697561</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>28048.0309852233</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>28851.0538556511</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>32532.2083531551</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>31343.8984585258</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>32357.3698222489</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>34915.2980937016</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>41160.2168813171</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>38037.7651639587</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>37953.1377351808</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>45456.6039711084</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3925.26523401912</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4285.87721043147</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5357.12238600568</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5096.95552613895</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5582.71785844978</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6464.73769415185</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6785.97483760086</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7048.77559612775</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6651.34213657969</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6464.96224295817</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8501.53865421219</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12073.7266463589</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>15575.1179943011</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>17161.86685621</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12781.9039134728</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11673.3258842491</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>12562.4332382961</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>13548.5971474789</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14416.7155599072</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>13864.5515986586</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>15387.5386290057</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14412.8525318407</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>15754.5387017698</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>17297.9273861954</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>17562.6948377256</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>17962.5365037733</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>18167.8818789915</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>169857.834476717</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>198065.806040171</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>265054.035538176</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>292227.472245097</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>342813.964568061</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>440149.557816257</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>472899.469796524</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>452175.381333986</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>336633.203428732</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>315626.665281696</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>350989.38549884</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>371039.695369626</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>348020.332168772</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>336071.049622191</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>275595.618826377</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>327370.54910382</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>351121.605053912</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>353875.813814656</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>360179.759434234</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>360861.204423394</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>450166.701084637</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>346366.472092868</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>370065.041784847</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>356274.241090623</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>395354.313725073</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>399403.56424292</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>397732.411402542</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1883.06718826906</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2139.33999123148</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2252.91293464459</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2397.64164934066</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2885.94406109832</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3177.47646543012</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3256.47261173509</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3520.27843847743</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3629.65962586812</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3312.91858721643</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3635.74884979753</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3879.83513922131</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3888.34084900133</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4240.04569735125</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4450.73477695582</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4474.24722130261</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4926.75673264062</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4867.93546020936</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5153.64668409884</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5346.97008130272</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5315.92943592823</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6864.454530293</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6962.37766822525</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7784.56955960972</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>7903.49684770474</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6864.39890742375</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>9412.80314282596</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>243168.946989831</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>249762.760330434</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>258149.463959375</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>301308.948274966</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>299221.29777587</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>329875.828619877</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>354929.227812545</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>373132.661249129</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>376085.635058162</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>392362.484229273</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>400464.574566221</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>421759.797859433</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>440712.45976561</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>467805.23316145</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>475574.447638159</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>467790.006616282</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>474174.868258794</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>476378.925497253</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>472975.33434893</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>512834.53082035</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>502182.716046909</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>512978.793215515</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>542215.046824699</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>560505.172883248</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>593955.90307005</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>607419.810636322</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>650362.907544438</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>74520.0119086385</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>86519.7434401108</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>92294.8740842175</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>100908.744711348</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>101157.099648326</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>117639.982468038</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>137796.577865996</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>137677.51466733</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>117773.377430556</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>116069.585001564</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>143339.951116322</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>164057.782501511</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>182079.523133694</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>232944.818156171</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>186711.785289677</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>217166.630240699</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>228656.693551897</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>231264.328503148</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>232362.778336248</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>247035.397957675</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>258915.364300976</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>247788.384197679</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>285571.327935213</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>292806.705642847</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>313513.634719272</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>327415.463563197</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>342695.324682101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>67591.6887730842</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>73482.7300540375</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>78472.2753867382</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>84375.8632096185</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>92166.2085286687</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>103859.709863596</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>109117.410943202</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>114751.973989951</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>119293.557400584</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>123010.16240398</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>129598.189365468</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>136667.939960441</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>143210.733880426</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>147829.328459163</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>144258.515553118</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>146993.168675774</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>145535.116982817</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>138257.627105656</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>140382.769244845</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>141261.705109636</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>147328.480737726</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>153007.920253096</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>173445.537930394</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>170779.407210664</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>176711.823122714</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>180110.684003173</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>181422.311436819</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>20220.556507372</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>20488.4538332231</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>23113.4277626922</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>27774.8024663788</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>26044.573337093</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>32495.5058142712</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>32350.0766284633</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>34180.2894367512</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>35527.6976515179</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>40350.6511769456</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>52987.305915443</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>64350.3802293215</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>87216.0485604221</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>105184.933716962</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>85209.3287090859</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>70982.5607918033</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>72404.8696595317</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>82456.7787147499</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>85015.3591092699</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>90925.2909363821</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>94326.4722246506</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>95184.8232756216</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>121742.874913064</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>136295.178491234</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>129763.60288743</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>142665.598910231</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>141201.769408935</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>186096.750801606</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>186936.311061584</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>210433.638066164</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>143863.569920791</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>103068.299945539</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>148237.495486873</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>184703.574018861</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>202103.02001229</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>202824.213055286</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>254154.589915118</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>351648.876255723</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>471501.763210428</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>551081.452750938</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>623741.16259472</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>494817.806263085</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>681107.841629221</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>868218.624124367</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>1065926.29669767</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>1117376.18813037</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>972560.085746336</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>771644.870330704</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>712003.956420926</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>878092.329401981</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>837912.452138994</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>939413.939071316</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>955627.928425286</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>946091.34632861</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>10569.6432488979</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11720.1010040471</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>14162.5178340331</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13954.6219281486</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>12648.7755471314</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15764.9358632358</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15148.0598365067</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>17258.0336410922</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>20225.5855192421</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>21149.3629405559</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>26053.1570507822</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>28102.7808711236</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>36020.4072061507</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>38518.8805085469</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>39189.3046603139</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>43351.4897552323</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>44973.6828581277</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>47105.6222038905</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>44708.8329219687</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>49281.5877529581</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>49669.8133954904</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>46444.8962582173</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>53805.7498910131</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>50526.4159257202</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>53426.4669665078</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>60022.6078772311</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>64377.1921277625</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14831.1094244595</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15005.4371222249</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15825.4915711832</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>16942.7648175216</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>18290.973388081</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>18576.8355911716</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>21694.9017777977</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>22303.7223234667</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>22948.2889613731</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>24311.7081870474</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>25319.5712679449</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>26831.1516460032</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>29380.114346924</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>31494.2939983561</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>31516.0138866074</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>32700.7525994904</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>32332.1590671182</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>31517.8419814692</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>32227.9588782521</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>32808.1829661015</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>33924.0432499866</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>34291.5571627396</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>36938.7698136963</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>39333.2821353173</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>40724.488061406</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>44421.6907605218</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>45808.4534376981</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>182517.490000644</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>216214.428284647</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>217664.653582738</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>228026.055508953</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>240511.084635492</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>271893.466428816</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>288102.393238667</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>300620.590774071</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>301534.779630259</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>296078.941511846</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>297012.355450662</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>317353.137226475</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>339998.727849272</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>341633.286004256</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>313655.576488803</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>348793.223615453</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>402216.32275118</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>413439.02365731</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>426353.792175192</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>417818.730415725</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>455877.510530322</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>448922.836141996</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>463903.29817032</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>482761.64579129</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>488706.972146397</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>481648.751875418</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>506535.716406962</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>50605.8870448203</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>61023.6526470002</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>71313.6906549056</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>75431.6347299638</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>80335.9539079763</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>102930.565415755</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>82676.9376260663</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>100358.767777082</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>115516.880123903</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>144135.256527149</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>187276.159905342</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>212706.661142875</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>247231.174522565</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>262633.308427856</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>228573.918089793</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>340295.214886689</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>329058.439192716</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>375203.183765347</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>403233.01600755</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>405904.604736011</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>447219.307004977</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>452957.432281731</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>446984.71802667</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>396347.951355496</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>412090.486415926</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>415938.620446496</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>482404.24535284</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>156486.615581622</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>175669.367950381</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>194709.651407188</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>193978.010886309</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>195088.992113511</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>274271.974272982</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>235338.043492557</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>226557.097189863</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>202183.774451127</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>198043.487418386</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>199150.171416948</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>196973.473133267</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>164271.619960723</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>159243.000176709</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>144314.497578266</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>181772.801576617</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>225527.191484974</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>243949.220790373</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>214091.114094722</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>230849.621579195</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>224988.649351701</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>251339.95735394</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>254827.746856389</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>238505.043280387</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>274259.997078361</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>247454.493276498</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>262200.809324289</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>4921276.99587354</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.656</t>
+          <t>5341150.50139217</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>6336426.9494057</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4.743</t>
+          <t>6916269.2275055</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.322</t>
+          <t>7769187.90614226</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6.372</t>
+          <t>9340715.63891083</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7.113</t>
+          <t>10361253.2747673</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6.828</t>
+          <t>9948619.40798997</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>5.658</t>
+          <t>8322979.86869321</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8304366.89318932</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>5.763</t>
+          <t>8513417.24005019</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>6.343</t>
+          <t>9290125.46157631</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>6.126</t>
+          <t>8956069.66988413</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>5.754</t>
+          <t>8464801.19380979</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>6.076</t>
+          <t>9024640.82415185</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>9234864.96040742</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>5.966</t>
+          <t>8873619.02842426</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>7.262</t>
+          <t>10735205.0690376</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>6.708</t>
+          <t>9984270.57396883</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>10260733.9137826</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>9.053</t>
+          <t>13323148.8208155</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>9.344</t>
+          <t>13738383.9776574</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>9.729</t>
+          <t>14527796.5703106</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>9.904</t>
+          <t>14771121.1889432</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>10.506</t>
+          <t>15467549.3582107</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10.695</t>
+          <t>15756482.0534959</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>11.255</t>
+          <t>16779863.4120609</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>13.061</t>
+          <t>18839927.3381845</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13.623</t>
+          <t>19515870.3478496</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>15.042</t>
+          <t>21781207.5677877</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15.458</t>
+          <t>22088209.8223135</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>16.975</t>
+          <t>24402627.602647</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>29247109.553696</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>20.793</t>
+          <t>30184421.5317737</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20.319</t>
+          <t>29176901.6484656</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18.742</t>
+          <t>26887461.4385939</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>18.866</t>
+          <t>27178762.915221</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>20.117</t>
+          <t>29207197.2599662</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>21.722</t>
+          <t>31539321.4309894</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>22.117</t>
+          <t>32077764.3699587</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>22.528</t>
+          <t>32949290.5486919</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>23.107</t>
+          <t>33815395.5954899</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>25.969</t>
+          <t>38259761.0834794</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>27.335</t>
+          <t>40423380.5953364</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>30.455</t>
+          <t>45365957.5714653</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>29.889</t>
+          <t>44457564.1180814</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>30.539</t>
+          <t>45519658.9228999</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>35.036</t>
+          <t>52536884.9528768</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>53180878.5887684</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>37.279</t>
+          <t>56228974.5039241</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>37.58</t>
+          <t>56741301.8515121</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>39.987</t>
+          <t>60297915.1357863</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>41.162</t>
+          <t>61927728.3661537</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>42.998</t>
+          <t>64906356.4569697</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9899.45809802025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10272.374094164</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11741.5407041449</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13621.9130440204</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13041.9288680172</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14374.8374379604</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15794.7994521949</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15165.3059844997</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16210.8110504593</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18414.4546374208</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20306.6265315877</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22043.1426313111</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24784.9265945763</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26888.8734107661</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26116.2311041288</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26652.186095027</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25286.9206351369</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24376.4015583748</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24804.1074921639</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25766.4844722728</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>26032.8185224329</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>27334.3121315087</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28884.5575778023</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>29329.9542193498</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30922.5204909022</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>30857.038153446</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>30787.7571581331</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>175229.528248466</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>174628.904151646</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>183548.083049689</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>189391.260094869</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>187442.190798599</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>198649.830319394</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>214882.097353427</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>225145.168315859</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>225111.3440502</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>220662.163760339</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>228436.784181492</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>240171.113557342</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>248627.712678455</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>261251.31497385</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>283295.312588047</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>304725.81084237</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>342798.77560853</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>374938.453773098</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>370067.651813713</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>366162.817231899</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>418317.907706488</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>419988.922253517</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>449302.102266205</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>396123.772409094</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>449183.104600414</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>411948.156769813</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>470220.167807605</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>78069.5851478296</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>83445.1053536972</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>90419.5271452468</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>89978.4537943947</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>98548.2577545835</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>111729.222149449</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>116693.284414281</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>129494.991911644</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>127170.297236136</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>128673.823629995</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>140886.888007287</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>155646.84801278</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>176865.705048684</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>188277.231540522</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>174474.051152227</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>199827.978008729</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>217058.319350043</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>236838.359959911</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>262086.360823724</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>257737.432560524</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>222193.781435508</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>224636.542950735</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>226859.539387775</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>228850.727608539</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>232433.642654016</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>246011.675742251</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>250141.727022035</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>83182.8012200634</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>81600.3425586891</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>91120.6972249038</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>81865.8944252988</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>87263.2639763285</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>98770.839307522</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>86372.129479571</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>78242.3404691636</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>101981.128813166</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>120100.327695967</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>131915.443354196</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>135693.864856191</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>132697.820504332</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>118586.389996473</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>125523.65316716</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>166231.853252965</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>171135.166183607</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>173892.369476723</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>154984.100965135</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>143985.59115563</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>153259.421336253</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>134654.476666987</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>164239.730173721</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>167163.136964405</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>169674.153665629</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>171259.736820849</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>171948.939648722</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>582459.652803746</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>655508.542549138</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>727508.773910537</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>660881.754495499</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>710974.412269718</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>859268.937660909</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>870594.804644848</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>883259.722784698</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>821593.429971069</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>823217.663937345</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>919073.029959849</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>1054094.82542112</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1164745.52333473</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>1186982.05790918</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1242815.90297359</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1551833.03243212</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1710505.30344963</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1994634.86902034</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>2038115.74344088</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>2158668.07099103</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>2426261.43343581</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>2565238.41231016</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>2726908.34597114</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>2671493.80102604</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2.022</t>
+          <t>2981007.74027622</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>3054532.59846986</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>2.245</t>
+          <t>3216295.43158215</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>519779.987636167</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>555233.317008705</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>672165.473937716</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>707259.181564844</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>716704.380747777</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>839429.411798469</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>878004.589099607</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>656648.029606541</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>572800.250638421</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>609623.871750875</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>726237.843815244</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>832968.919350023</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>896650.670127539</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>997707.145048706</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>1031919.80267916</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>1274154.16896441</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>1357024.58922399</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>1625504.52250924</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>1634975.555172</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>1621988.63354295</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>1942825.98910646</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1835725.89813493</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>1.196</t>
+          <t>1925805.46044705</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>1761404.79200587</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>1.079</t>
+          <t>1744410.75190423</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>1737303.87361693</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>1776364.97616706</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>87217.4011704634</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>88212.9925310794</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>97957.4744710881</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>91033.6499575653</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>78733.2848592136</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>84204.1781212518</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>103803.497577904</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>113034.688197105</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>111821.340167651</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>124829.416916465</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>148833.793988687</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>183386.924703425</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>216146.335385941</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>244997.862868774</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>182141.163346158</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>215762.763039563</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>238064.816793387</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>264065.13784472</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>274371.732712263</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>245609.188571119</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>225755.951279672</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>227462.369317126</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>253114.36025543</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>265800.991599897</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>297887.998269403</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>303264.244306462</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>326512.587927545</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>227720.213333614</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>256042.832206501</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>286362.097447276</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>297342.43125125</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>317737.228515804</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>379839.83416021</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>403899.871389453</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>414189.644178522</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>399390.301389993</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>432665.376008947</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>515512.900822123</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>606328.362389758</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>646807.888582447</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>757790.947477592</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>714202.581051784</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>843464.697098324</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>952384.313641841</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1053714.34721384</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>1098639.01092006</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1156440.16047126</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>1243109.31699867</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>1177781.80006963</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>1187787.16941904</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>1223970.43548487</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>1337978.35153766</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>1385801.7583792</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1435260.35979208</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>377818.048363014</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>435384.031198241</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>500955.078108746</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>494603.551452046</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>556895.418195371</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>713329.189382971</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>711453.360283611</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>742664.599163248</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>668074.773620159</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>701203.827012395</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>844401.869962787</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>974367.124226305</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>1074123.53137698</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>1234588.65050334</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1214528.10678077</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>1467011.1006295</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>1669174.13656473</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1941283.18377248</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1884127.50804715</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1907020.96190876</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>1.186</t>
+          <t>2075848.63700445</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>2079727.87332559</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>2119179.48890612</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>2198042.00057435</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>1.434</t>
+          <t>2512917.14067812</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>1.476</t>
+          <t>2568200.82702584</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>1.517</t>
+          <t>2642209.93503747</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>gdp.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
